--- a/output/pdf_financials_xlsx/GIL.xlsx
+++ b/output/pdf_financials_xlsx/GIL.xlsx
@@ -3057,22 +3057,22 @@
         <v>11.034</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>41.291</v>
+        <v>23.784</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>42.934</v>
+        <v>45.774</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>62.092</v>
+        <v>65.983</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>77.377</v>
+        <v>79.066</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>77.06399999999999</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>110.105</v>
+        <v>114.737</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>163.662</v>
@@ -3084,7 +3084,7 @@
         <v>106.964</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>140.271</v>
+        <v>1099.584</v>
       </c>
     </row>
     <row r="49">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">

--- a/output/pdf_financials_xlsx/GIL.xlsx
+++ b/output/pdf_financials_xlsx/GIL.xlsx
@@ -6662,19 +6662,19 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.542</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>15.649</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>5.783</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="N112" s="3" t="n">
         <v>0</v>
@@ -31218,7 +31218,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GIL.xlsx
+++ b/output/pdf_financials_xlsx/GIL.xlsx
@@ -1307,7 +1307,7 @@
         <v>9.984</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>4.091</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-17.375</v>
@@ -1535,10 +1535,8 @@
       <c r="L20" s="3" t="n">
         <v>259.809</v>
       </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M20" s="3" t="n">
+        <v>-225.282</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>607.183</v>
@@ -1703,7 +1701,7 @@
         <v>259.809</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>-229.373</v>
+        <v>-225.282</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>607.183</v>
@@ -1876,7 +1874,7 @@
         <v>204.574016</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>201.204386</v>
+        <v>197.615789</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>197.779479</v>
@@ -2155,7 +2153,7 @@
         <v>3.996397478234765</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.783557785789958</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>2.781967407350478</v>
@@ -2210,7 +2208,7 @@
         <v>9.200357944559672</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>-11.5770341941254</v>
+        <v>-11.37055109939251</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>20.7756529356012</v>
@@ -4353,22 +4351,22 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>14.518</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>15.884</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>15.29</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>13.828</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>17.749</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>59.759</v>
       </c>
     </row>
     <row r="71">
@@ -4410,22 +4408,22 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>14.518</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>15.884</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>15.29</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>150</v>
+        <v>163.828</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>300</v>
+        <v>317.749</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>450</v>
+        <v>509.759</v>
       </c>
     </row>
     <row r="72">
@@ -4638,22 +4636,22 @@
         <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>15.773</v>
+        <v>1.255</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>15.884</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>23.202</v>
+        <v>7.912</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>20.465</v>
+        <v>6.637</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>47.417</v>
+        <v>29.668</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>521.446</v>
+        <v>461.687</v>
       </c>
     </row>
     <row r="76">
@@ -4809,22 +4807,22 @@
         <v>0</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0</v>
+        <v>66.982</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>66.58</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>93.812</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>0</v>
+        <v>80.16200000000001</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>0</v>
+        <v>99.67100000000001</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>0</v>
+        <v>254.742</v>
       </c>
     </row>
     <row r="79">
@@ -4866,22 +4864,22 @@
         <v>669</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>845</v>
+        <v>911.982</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>1000</v>
+        <v>1066.58</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>600</v>
+        <v>693.812</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>780</v>
+        <v>860.162</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>1235.87</v>
+        <v>1335.541</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>3863.68</v>
+        <v>4118.422</v>
       </c>
     </row>
     <row r="80">
@@ -4925,22 +4923,22 @@
         <v>0.3455450003925474</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.4606174781710924</v>
+        <v>0.5050438976633339</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.6414791997162096</v>
+        <v>0.6943781404416071</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.3125968724682909</v>
+        <v>0.3694384457683501</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.4941126215490484</v>
+        <v>0.5440498745591505</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>1.054384337772054</v>
+        <v>1.134993900392064</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>1.210952380551347</v>
+        <v>1.299240277343826</v>
       </c>
     </row>
     <row r="81">
@@ -5959,7 +5957,7 @@
         <v>259.809</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>-229.373</v>
+        <v>-225.282</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>607.183</v>
@@ -6164,22 +6162,22 @@
         <v>-1.098</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>-1.863</v>
+        <v>-10.007</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-5.227</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-13.807</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>-8.32</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>-34.801</v>
       </c>
       <c r="N103" s="3" t="n">
         <v>0</v>
@@ -6329,22 +6327,22 @@
         <v>0.243</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-179.868</v>
+        <v>-188.012</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>27.459</v>
+        <v>34.529</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>86.47799999999999</v>
+        <v>81.251</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-2.793</v>
+        <v>-16.6</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-68.976</v>
+        <v>-77.29600000000001</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>383.058</v>
+        <v>348.257</v>
       </c>
       <c r="N106" s="3" t="n">
         <v>0</v>
@@ -6861,52 +6859,52 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-11.59</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-1.061</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-1.026</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-4.776</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-5.439</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-4.315</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-6.15</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-10.833</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-2.845</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-17.566</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-11.558</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-7.67</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-2.766</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-5.426</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-5.02</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-7.371</v>
       </c>
     </row>
     <row r="117">
@@ -7136,7 +7134,7 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-0.012</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -7145,10 +7143,10 @@
         <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-2.152</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-5.99</v>
       </c>
       <c r="G121" s="3" t="n">
         <v>0</v>
@@ -9538,7 +9536,11 @@
           <t>Current portion of lease obligations (note 10(b))</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -9984,7 +9986,11 @@
           <t>Lease obligations (note 10(b))</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -12554,7 +12560,11 @@
           <t>Current portion of lease obligations (note 10(b)) 14,161</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -12950,7 +12960,11 @@
           <t>Lease obligations (note 10(b)) 83,900</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -15244,7 +15258,11 @@
           <t>Current portion of lease obligations (note 9(b))</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -15426,7 +15444,11 @@
           <t>Lease obligations (note 9(b))</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -22854,7 +22876,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E159" s="5" t="n">
         <v>-11.59</v>
       </c>
@@ -26208,7 +26234,11 @@
           <t>Purchase of intangible assets (4,720)</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -30876,7 +30906,11 @@
           <t>Prepaid expenses, deposits and other current assets</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -38030,7 +38064,11 @@
           <t>Repurchase of shares (note 15(e))</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -39436,7 +39474,11 @@
           <t>Future income taxes (note 14)</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E336" s="5" t="n">
         <v>-15.885</v>
       </c>
@@ -40470,7 +40512,11 @@
           <t>Repurchase of shares</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E347" s="5" t="n">
         <v>-0.012</v>
       </c>
@@ -47474,7 +47520,11 @@
           <t>Income tax recovery (note 18)</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -47568,7 +47618,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -48228,7 +48282,11 @@
           <t>Income tax (recovery) expense (note 18)</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>
@@ -52526,7 +52584,11 @@
           <t>Income tax recovery (note 20)</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
